--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -59,7 +59,7 @@
     <t/>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-observation-code-vs (extensible)</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-observation-code-vs (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
